--- a/Decks/4cRash.xlsx
+++ b/Decks/4cRash.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F0D2A6-EE13-434A-9C3A-4C6D0F95DFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/Decks/4cRash.xlsx
+++ b/Decks/4cRash.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F0D2A6-EE13-434A-9C3A-4C6D0F95DFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC13709-B83D-459F-9052-98B3676B2687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
   </bookViews>
   <sheets>
     <sheet name="4cRash" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="107">
   <si>
     <t>Função</t>
   </si>
@@ -354,13 +354,16 @@
   </si>
   <si>
     <t>Countersquall</t>
+  </si>
+  <si>
+    <t>https://www.ligamagic.com.br/?view=dks/deck&amp;id=10019715</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +387,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -402,10 +413,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -422,8 +434,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -745,7 +761,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75126D7-ABA5-4289-B680-4F61CC44A6A6}">
   <sheetPr codeName="Planilha32"/>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="4" customWidth="1"/>
@@ -754,9 +770,10 @@
     <col min="4" max="4" width="41.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -775,8 +792,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -791,7 +811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -806,7 +826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -821,7 +841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -836,7 +856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -851,7 +871,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -866,7 +886,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -881,7 +901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -896,7 +916,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -911,7 +931,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -926,7 +946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -941,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -956,7 +976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -971,7 +991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -986,7 +1006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2318,8 +2338,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G1" r:id="rId1" xr:uid="{C0DCA42E-3093-4743-AA64-4A9381530AA6}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Decks/4cRash.xlsx
+++ b/Decks/4cRash.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC13709-B83D-459F-9052-98B3676B2687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6961C1-125E-471E-B684-D45C4CE19535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
   </bookViews>
   <sheets>
     <sheet name="4cRash" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="104">
   <si>
     <t>Função</t>
   </si>
@@ -299,9 +299,6 @@
     <t>Heartless Act</t>
   </si>
   <si>
-    <t>Languish</t>
-  </si>
-  <si>
     <t>Zhur-Taa Druid</t>
   </si>
   <si>
@@ -314,9 +311,6 @@
     <t>Energy Flux</t>
   </si>
   <si>
-    <t>Fatespinner</t>
-  </si>
-  <si>
     <t>Curtains' Call</t>
   </si>
   <si>
@@ -354,16 +348,13 @@
   </si>
   <si>
     <t>Countersquall</t>
-  </si>
-  <si>
-    <t>https://www.ligamagic.com.br/?view=dks/deck&amp;id=10019715</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,14 +378,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -413,11 +396,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -434,12 +416,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -761,7 +739,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75126D7-ABA5-4289-B680-4F61CC44A6A6}">
   <sheetPr codeName="Planilha32"/>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="4" customWidth="1"/>
@@ -770,10 +748,9 @@
     <col min="4" max="4" width="41.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,11 +769,8 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -811,7 +785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -826,7 +800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -835,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -856,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -865,13 +839,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -886,7 +860,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -901,7 +875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -916,7 +890,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -931,7 +905,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -946,7 +920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -961,7 +935,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -976,7 +950,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -991,7 +965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1006,7 +980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1405,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>21</v>
@@ -1435,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1465,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>24</v>
@@ -1561,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>29</v>
@@ -1593,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F54"/>
     </row>
@@ -1689,10 +1663,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1800,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>45</v>
@@ -1817,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1863,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>48</v>
@@ -1882,7 +1856,7 @@
         <v>85</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -1941,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2016,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>57</v>
@@ -2044,10 +2018,10 @@
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>59</v>
@@ -2076,13 +2050,13 @@
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F85" s="4"/>
     </row>
@@ -2111,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>73</v>
@@ -2338,11 +2312,8 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G1" r:id="rId1" xr:uid="{C0DCA42E-3093-4743-AA64-4A9381530AA6}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Decks/4cRash.xlsx
+++ b/Decks/4cRash.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6961C1-125E-471E-B684-D45C4CE19535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB6B801-5519-42EB-97C7-2C6B039C945B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
   </bookViews>
@@ -182,9 +182,6 @@
     <t>Assassin's Trophy</t>
   </si>
   <si>
-    <t>Abrupt Decay</t>
-  </si>
-  <si>
     <t>Rakdos Charm</t>
   </si>
   <si>
@@ -224,130 +221,133 @@
     <t>Suport</t>
   </si>
   <si>
-    <t>Exsanguinate</t>
+    <t>Black Waltz No. 3</t>
+  </si>
+  <si>
+    <t>Coruscation Mage</t>
+  </si>
+  <si>
+    <t>Kess, Dissident Mage</t>
+  </si>
+  <si>
+    <t>Fiery Inscription</t>
+  </si>
+  <si>
+    <t>Witherbloom Apprentice</t>
+  </si>
+  <si>
+    <t>The Lord of Pain</t>
+  </si>
+  <si>
+    <t>Niv-Mizzet, Parun</t>
+  </si>
+  <si>
+    <t>Mizzix's Mastery</t>
+  </si>
+  <si>
+    <t>Rashmi, Eternities Crafter</t>
+  </si>
+  <si>
+    <t>Exalted Flamer of Tzeentch</t>
+  </si>
+  <si>
+    <t>Lindblum, Industrial Regency // Mage Siege</t>
+  </si>
+  <si>
+    <t>Devastation Tide</t>
+  </si>
+  <si>
+    <t>Arboria</t>
+  </si>
+  <si>
+    <t>God-Eternal Kefnet</t>
+  </si>
+  <si>
+    <t>Cultivate</t>
+  </si>
+  <si>
+    <t>Bala Ged Recovery</t>
+  </si>
+  <si>
+    <t>Curtains' Call</t>
+  </si>
+  <si>
+    <t>Mob</t>
+  </si>
+  <si>
+    <t>Game Over</t>
+  </si>
+  <si>
+    <t>Elemental Teachings</t>
+  </si>
+  <si>
+    <t>Proctor's Gaze</t>
+  </si>
+  <si>
+    <t>Embrace the Paradox</t>
+  </si>
+  <si>
+    <t>Countersquall</t>
+  </si>
+  <si>
+    <t>Path of Ancestry</t>
+  </si>
+  <si>
+    <t>Yavimaya Coast</t>
+  </si>
+  <si>
+    <t>Llanowar Wastes</t>
+  </si>
+  <si>
+    <t>Shivan Reef</t>
+  </si>
+  <si>
+    <t>Sunken Hollow</t>
+  </si>
+  <si>
+    <t>Hinterland Harbor</t>
+  </si>
+  <si>
+    <t>Deathcap Glade</t>
+  </si>
+  <si>
+    <t>Ping</t>
+  </si>
+  <si>
+    <t>Thor, God of Thunder</t>
+  </si>
+  <si>
+    <t>The Frightful Four</t>
+  </si>
+  <si>
+    <t>Alela, Cunning Conqueror</t>
   </si>
   <si>
     <t>Guttersnipe</t>
   </si>
   <si>
-    <t>Electrostatic Field</t>
-  </si>
-  <si>
-    <t>Black Waltz No. 3</t>
-  </si>
-  <si>
-    <t>Coruscation Mage</t>
-  </si>
-  <si>
-    <t>Kess, Dissident Mage</t>
-  </si>
-  <si>
-    <t>Fiery Inscription</t>
-  </si>
-  <si>
-    <t>Witherbloom Apprentice</t>
-  </si>
-  <si>
-    <t>The Lord of Pain</t>
-  </si>
-  <si>
-    <t>Niv-Mizzet, Parun</t>
-  </si>
-  <si>
-    <t>Professor Onyx</t>
-  </si>
-  <si>
-    <t>Fandaniel, Telophoroi Ascian</t>
-  </si>
-  <si>
-    <t>Displacer Kitten</t>
-  </si>
-  <si>
-    <t>Mizzix's Mastery</t>
-  </si>
-  <si>
-    <t>Rashmi, Eternities Crafter</t>
-  </si>
-  <si>
-    <t>Exalted Flamer of Tzeentch</t>
-  </si>
-  <si>
-    <t>Lindblum, Industrial Regency // Mage Siege</t>
-  </si>
-  <si>
-    <t>Devastation Tide</t>
-  </si>
-  <si>
-    <t>Arboria</t>
-  </si>
-  <si>
     <t>Firebrand Archer</t>
   </si>
   <si>
-    <t>God-Eternal Kefnet</t>
-  </si>
-  <si>
-    <t>Cultivate</t>
-  </si>
-  <si>
-    <t>Bala Ged Recovery</t>
-  </si>
-  <si>
-    <t>Aetherspouts</t>
+    <t>Elotrastitic Field</t>
+  </si>
+  <si>
+    <t>Zhur-Taa Druid</t>
+  </si>
+  <si>
+    <t>Quandrix, the Proof</t>
+  </si>
+  <si>
+    <t>Street Spasm</t>
+  </si>
+  <si>
+    <t>Expansion // Explosion</t>
   </si>
   <si>
     <t>Heartless Act</t>
   </si>
   <si>
-    <t>Zhur-Taa Druid</t>
-  </si>
-  <si>
-    <t>Parcelbeast</t>
-  </si>
-  <si>
-    <t>Mana Maze</t>
-  </si>
-  <si>
-    <t>Energy Flux</t>
-  </si>
-  <si>
-    <t>Curtains' Call</t>
-  </si>
-  <si>
-    <t>Embodiment of Spring</t>
-  </si>
-  <si>
-    <t>Mob</t>
-  </si>
-  <si>
-    <t>Game Over</t>
-  </si>
-  <si>
-    <t>Evolving Wilds</t>
-  </si>
-  <si>
-    <t>Maestros Theater</t>
-  </si>
-  <si>
-    <t>Elemental Teachings</t>
-  </si>
-  <si>
-    <t>Street Spasm</t>
-  </si>
-  <si>
-    <t>Quiet Contemplation</t>
-  </si>
-  <si>
-    <t>Proctor's Gaze</t>
-  </si>
-  <si>
-    <t>Embrace the Paradox</t>
-  </si>
-  <si>
-    <t>Expansion // Explosion</t>
-  </si>
-  <si>
-    <t>Countersquall</t>
+    <t>Lethal Scheme</t>
   </si>
 </sst>
 </file>
@@ -806,10 +806,10 @@
       </c>
       <c r="B4" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -944,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,14 +970,14 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C15&lt;&gt;D15</f>
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -985,14 +985,14 @@
         <v>9</v>
       </c>
       <c r="B16" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C16&lt;&gt;D16</f>
         <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1000,14 +1000,14 @@
         <v>9</v>
       </c>
       <c r="B17" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C17&lt;&gt;D17</f>
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1376,10 +1376,10 @@
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>21</v>
@@ -1409,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1436,10 +1436,10 @@
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>24</v>
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1535,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>29</v>
@@ -1567,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F54"/>
     </row>
@@ -1660,13 +1660,13 @@
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1726,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>41</v>
@@ -1771,10 +1771,10 @@
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>45</v>
@@ -1791,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1834,13 +1834,13 @@
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="F71" s="4"/>
     </row>
@@ -1850,13 +1850,13 @@
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F74" s="4"/>
     </row>
@@ -1899,10 +1899,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F75" s="4"/>
     </row>
@@ -1915,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -1945,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -1960,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -1975,341 +1975,341 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>55</v>
+      </c>
+      <c r="B81" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B81" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="F81"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B87" s="5" t="b">
-        <f>C87&lt;&gt;D87</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F87"/>
+      <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B88" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C88&lt;&gt;D88</f>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F88" s="4"/>
+        <v>69</v>
+      </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C89&lt;&gt;D89</f>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F89"/>
+        <v>74</v>
+      </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C90&lt;&gt;D90</f>
+        <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D90" t="s">
-        <v>77</v>
+      <c r="D90" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D92" t="s">
+        <v>70</v>
+      </c>
+      <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C93&lt;&gt;D93</f>
+        <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="D94" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F96"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F97"/>
+        <v>66</v>
+      </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E99" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="F99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>82</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E101" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -2329,7 +2329,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C101</xm:sqref>
+          <xm:sqref>C2:C3 C5:C11 C15:C22 C24:C89 C91:C101</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Decks/4cRash.xlsx
+++ b/Decks/4cRash.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB6B801-5519-42EB-97C7-2C6B039C945B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D585AF8-2B41-42E7-B010-1713EC0EB7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
   </bookViews>
@@ -836,10 +836,10 @@
       </c>
       <c r="B6" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
